--- a/Clustering-Akun-LokaKin.xlsx
+++ b/Clustering-Akun-LokaKin.xlsx
@@ -3883,7 +3883,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21T11:57:47</t>
+          <t>2026-10-21T12:32:46</t>
         </is>
       </c>
     </row>

--- a/Clustering-Akun-LokaKin.xlsx
+++ b/Clustering-Akun-LokaKin.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Panduan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Isi Peran'!$A$4:$M$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Snapshot Database'!$A$1:$J$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Isi Peran'!$A$4:$M$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Snapshot Database'!$A$1:$J$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -646,37 +646,41 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>staff-1</t>
+          <t>kepala-1</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Edwin, S.Sos</t>
+          <t>Heru Herlambang, S.AP</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>1801010101010001</t>
+          <t>198107192003121000</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Staf</t>
+          <t>Kepala Loka</t>
         </is>
       </c>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5" t="inlineStr"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Umum; Layanan Rehabilitasi Medis; Layanan Rehabilitasi Sosial; Clinical Supervisor</t>
+        </is>
+      </c>
       <c r="M5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -685,37 +689,41 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>staff-2</t>
+          <t>staff-1</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Nurma Fitria, S.IP, M.IKom</t>
+          <t>Edwin, S.Sos</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>198611232010012008</t>
+          <t>197608242008011000</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Umum</t>
+          <t>Layanan Rehabilitasi Sosial</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Staf</t>
+          <t>Ketua Tim</t>
         </is>
       </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Sosial</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
@@ -724,22 +732,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>staff-3</t>
+          <t>staff-2</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>dr. Heni Purwanti</t>
+          <t>Nurma Fitria, S.IP, M.IKom</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>197501012005012003</t>
+          <t>198602262014032000</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -756,7 +764,7 @@
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr"/>
@@ -767,38 +775,42 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>staff-4</t>
+          <t>staff-3</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Saiful Bahri, A.Md.Kep</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+          <t>dr. Heni Purwanti</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>199202112019022000</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Sarana &amp; Prasarana</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Staf</t>
+          <t>Ketua Tim</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="J8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Medis</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -806,18 +818,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>staff-5</t>
+          <t>staff-4</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Okta Delvianita, AMKL, SE.</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
+          <t>Saiful Bahri, A.Md.Kep</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>198401012010011000</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Bendahara</t>
+          <t>Sarana &amp; Prasarana</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -833,11 +849,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -845,18 +857,22 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>staff-6</t>
+          <t>staff-5</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Ns. Hamsah Prihadi Istianto, S.Kep</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
+          <t>Okta Delvianita, S.M</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>199010202014032000</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Clinical Supervisor</t>
+          <t>Bendahara</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -872,11 +888,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -884,38 +896,42 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>staff-7</t>
+          <t>staff-6</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>dr. Utari Gita Mutiara</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
+          <t>Ns. Hamsah Prihadi Istianto, S.Kep</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>198902122014031000</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Clinical Supervisor</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Staf</t>
+          <t>Clinical Supervisor</t>
         </is>
       </c>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Umum; Layanan Rehabilitasi Medis; Layanan Rehabilitasi Sosial</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -923,15 +939,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>staff-8</t>
+          <t>staff-7</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Yulina Destiani, A.Md.Kep</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
+          <t>dr. Utari Gita Mutiara</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>199107132020122000</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -950,11 +970,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -962,22 +978,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>staff-9</t>
+          <t>staff-8</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Daniel, A.Md.Kep</t>
+          <t>Yulina Destiani, A.Md.Kep</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>197804122006041005</t>
+          <t>199812122020122000</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1001,15 +1017,19 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>staff-10</t>
+          <t>staff-9</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Yoga Adi Yuliawan, A.Md.Kes</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
+          <t>Daniel, A.Md.Kep</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>199008092020121000</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Admin</t>
@@ -1028,11 +1048,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1040,18 +1056,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>staff-11</t>
+          <t>staff-10</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Evi Soleha, A.Md.AK</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
+          <t>Yoga Adi Yuliawan, A.Md.Kes</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>199707272022031000</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1067,11 +1087,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -1079,18 +1095,22 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>staff-12</t>
+          <t>staff-11</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Nanda Alif Utama, A.Md.RAD</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
+          <t>Evi Soleha, A.Md.AK</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>199411102023212000</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1106,11 +1126,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1118,18 +1134,22 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>staff-13</t>
+          <t>staff-12</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Risma Sefridasari, A.Md.KG</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
+          <t>Nanda Alif Utama, A.Md.RAD</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>199101202023211000</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Layanan Rehabilitasi Sosial</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1145,11 +1165,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -1157,15 +1173,19 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>staff-14</t>
+          <t>staff-13</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Tri Yunita, A.Md.Keb</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
+          <t>Risma Sefridasari, A.Md.KG</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>199008312023212000</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1184,11 +1204,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1196,15 +1212,19 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>staff-15</t>
+          <t>staff-14</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Dendi Purnama, S.Kep, Ns</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
+          <t>Tri Yunita, A.Md.Keb</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>199406222023212000</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1223,11 +1243,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -1235,15 +1251,19 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>staff-16</t>
+          <t>staff-15</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Randy Simanjutak, A.Md.Gz</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+          <t>Dendi Purnama, S.Kep, Ns</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>199012132023211000</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1262,11 +1282,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1274,18 +1290,22 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>staff-17</t>
+          <t>staff-16</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Ikke Asmawati, A.Md.KL</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
+          <t>Randy Simanjutak, A.Md.Gz</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>199105142023211000</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Perencanaan</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1301,11 +1321,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="5" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1313,18 +1329,22 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>staff-18</t>
+          <t>staff-17</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>dr. Resti Adystia</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
+          <t>Ikke Asmawati, A.Md.KL</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>199512102023212000</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Perencanaan</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1340,11 +1360,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1352,15 +1368,19 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>staff-19</t>
+          <t>staff-18</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Karunia Hadpha Saputri, A.Md.Keb</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
+          <t>dr. Resti Adystia</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>198709232023212000</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1379,11 +1399,7 @@
         <v>1</v>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -1391,15 +1407,19 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>staff-20</t>
+          <t>staff-19</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Wiria Ahaddillah, S.Kep, Ners</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
+          <t>Karunia Hadpha Saputri, A.Md.Keb</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>199012092023212000</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1418,11 +1438,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1430,15 +1446,19 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>staff-21</t>
+          <t>staff-20</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Heby Segapa, A.Md.Farm</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
+          <t>Wiria Ahaddillah, S.Kep, Ners</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>199501082023211000</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1457,11 +1477,7 @@
         <v>1</v>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1469,15 +1485,19 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>staff-22</t>
+          <t>staff-21</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Febri Ardiyansyah, AMF</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
+          <t>Heby Segapa, A.Md.Farm</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>199005072023211000</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1496,11 +1516,7 @@
         <v>1</v>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1508,15 +1524,19 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>staff-23</t>
+          <t>staff-22</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Anggi Oktaria, A.Md.Ft</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
+          <t>Febri Ardiyansyah, AMF</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>199302112023211000</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1535,11 +1555,7 @@
         <v>1</v>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -1547,15 +1563,19 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>staff-24</t>
+          <t>staff-23</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Pika Junetthy BR Pinem, A.Md.Gz</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
+          <t>Anggi Oktaria, A.Md.Ft</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>199810062023212000</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -1574,11 +1594,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -1586,18 +1602,22 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>staff-25</t>
+          <t>staff-24</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Galuh Dwi Satria Vianto, A.Md.Kep</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
+          <t>Pika Junetthy BR Pinem, A.Md.Gz</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>199606072023212000</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1613,11 +1633,7 @@
         <v>1</v>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -1625,18 +1641,22 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>staff-26</t>
+          <t>staff-25</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Yessy Lisnawati, SE</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
+          <t>Galuh Dwi Satria Vianto, A.Md.Kep</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>199203122023211000</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Umum</t>
+          <t>Layanan Rehabilitasi Sosial</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1652,11 +1672,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -1664,15 +1680,19 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>staff-27</t>
+          <t>staff-26</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Yudian Pratama Putra, S.M</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
+          <t>Yessy Lisnawati, SE</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>198811212025212000</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -1691,11 +1711,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -1703,15 +1719,19 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>staff-28</t>
+          <t>staff-27</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Restivo Nandami, A.Md</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n"/>
+          <t>Yudian Pratama Putra, S.M</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>199409292025211000</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -1730,11 +1750,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -1742,15 +1758,19 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>staff-29</t>
+          <t>staff-28</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Heti Liswati</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
+          <t>Restivo Nandami, A.Md</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>199109022025212000</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -1769,11 +1789,7 @@
         <v>1</v>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -1781,15 +1797,19 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>staff-30</t>
+          <t>staff-29</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Riza Rimayanti</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n"/>
+          <t>Heti Liswati</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>199404142025212000</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -1808,11 +1828,7 @@
         <v>1</v>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -1820,15 +1836,19 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>staff-31</t>
+          <t>staff-30</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Denda Nopriawan Putra</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n"/>
+          <t>Riza Rimayanti</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>199404012025212000</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -1847,11 +1867,7 @@
         <v>1</v>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -1859,15 +1875,19 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>staff-32</t>
+          <t>staff-31</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Ahmad Soleh, S.Kom</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n"/>
+          <t>Denda Nopriawan Putra</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>198911182025211000</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -1886,11 +1906,7 @@
         <v>1</v>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -1898,15 +1914,19 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>staff-33</t>
+          <t>staff-32</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Amardin Fikri, A.Md</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n"/>
+          <t>Ahmad Soleh, S.Kom</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>199106242025211000</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -1925,11 +1945,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -1937,15 +1953,19 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>staff-34</t>
+          <t>staff-33</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Evi Talia, A.Md</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n"/>
+          <t>Amardin Fikri, A.Md</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>198912072025211000</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -1964,11 +1984,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -1976,15 +1992,19 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>staff-35</t>
+          <t>staff-34</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Eka Rahma Saputri</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n"/>
+          <t>Evi Talia, A.Md</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>199412092025212000</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2003,11 +2023,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -2015,18 +2031,22 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>staff-36</t>
+          <t>staff-35</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Indra Gunawan</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n"/>
+          <t>Eka Rahma Saputri</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>1801064911980010</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2042,11 +2062,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -2054,15 +2070,19 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>staff-37</t>
+          <t>staff-36</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Amelia, A.Md.Kep</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n"/>
+          <t>Indra Gunawan</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>198809152025211000</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2081,11 +2101,7 @@
         <v>1</v>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -2093,15 +2109,19 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>staff-38</t>
+          <t>staff-37</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Adams Resmitha Thalib, SE</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n"/>
+          <t>Amelia, A.Md.Kep</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>199805032025212000</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2120,11 +2140,7 @@
         <v>1</v>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -2132,12 +2148,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>staff-39</t>
+          <t>staff-38</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Arisman</t>
+          <t>Adams Resmitha Thalib, SE</t>
         </is>
       </c>
       <c r="D43" s="5" t="n"/>
@@ -2171,15 +2187,19 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>staff-40</t>
+          <t>staff-39</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Rizal, S.Psi</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n"/>
+          <t>Arisman</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>198804112025211000</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2198,11 +2218,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -2210,15 +2226,19 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>staff-41</t>
+          <t>staff-40</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Yoga Eko Budiyanto</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n"/>
+          <t>Rizal, S.Psi</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>199510122025211000</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2237,11 +2257,7 @@
         <v>1</v>
       </c>
       <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -2249,15 +2265,19 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>staff-42</t>
+          <t>staff-41</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Raga Dwindo Pangestu</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n"/>
+          <t>Yoga Eko Budiyanto</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>199412292025211000</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2276,11 +2296,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -2288,15 +2304,19 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>staff-43</t>
+          <t>staff-42</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Wendy Ramarten, S.Pd</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n"/>
+          <t>Raga Dwindo Pangestu</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>199705052025211000</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2315,11 +2335,7 @@
         <v>1</v>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -2327,15 +2343,19 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>staff-44</t>
+          <t>staff-43</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Yoyon Saputra, S.Sos</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n"/>
+          <t>Wendy Ramarten, S.Pd</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>199608132025211000</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2354,11 +2374,7 @@
         <v>1</v>
       </c>
       <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -2374,7 +2390,11 @@
           <t>Indra Ibnul Alhibi Ramadhani, A.Md.Pi</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>1871131412000010</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2393,11 +2413,7 @@
         <v>1</v>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -2413,7 +2429,11 @@
           <t>Emi Rosmiko Sari, A.Md.Kep</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>198206112025212000</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -2432,11 +2452,7 @@
         <v>1</v>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -2452,7 +2468,11 @@
           <t>Saiful Hamdani, S.Psi</t>
         </is>
       </c>
-      <c r="D51" s="5" t="n"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>1871131508000000</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -2471,11 +2491,7 @@
         <v>1</v>
       </c>
       <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -2491,7 +2507,11 @@
           <t>M. Nur Hidayatullah</t>
         </is>
       </c>
-      <c r="D52" s="5" t="n"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>198607132025211000</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2510,11 +2530,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -2530,7 +2546,11 @@
           <t>Yusuf Arief Sena K, S.Psi</t>
         </is>
       </c>
-      <c r="D53" s="5" t="n"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>1871030806990000</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2549,11 +2569,7 @@
         <v>1</v>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -2569,7 +2585,11 @@
           <t>Suci Ramadani, AMKL</t>
         </is>
       </c>
-      <c r="D54" s="5" t="n"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>199004122025212000</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2588,11 +2608,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -2608,7 +2624,11 @@
           <t>Nadia Maulidia, A.Md.RMIK</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>1801065605020000</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Medis</t>
@@ -2627,11 +2647,7 @@
         <v>1</v>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -2647,7 +2663,11 @@
           <t>Nur Cholish</t>
         </is>
       </c>
-      <c r="D56" s="5" t="n"/>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>198312282025211000</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2666,11 +2686,7 @@
         <v>1</v>
       </c>
       <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -2686,7 +2702,11 @@
           <t>Gunawan Adi Saputra</t>
         </is>
       </c>
-      <c r="D57" s="5" t="n"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>199211112025211000</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2705,11 +2725,7 @@
         <v>1</v>
       </c>
       <c r="L57" s="5" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -2725,7 +2741,11 @@
           <t>Saipul Bahri</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>198505022025211000</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2744,11 +2764,7 @@
         <v>1</v>
       </c>
       <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -2764,7 +2780,11 @@
           <t>Septila Damirza</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>199509052025211000</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2783,11 +2803,7 @@
         <v>1</v>
       </c>
       <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -2803,7 +2819,11 @@
           <t>Ma'ruf Nufri Ismail</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>198711232025211000</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2822,11 +2842,7 @@
         <v>1</v>
       </c>
       <c r="L60" s="5" t="inlineStr"/>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -2842,7 +2858,11 @@
           <t>Mukhsinin</t>
         </is>
       </c>
-      <c r="D61" s="5" t="n"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>199412122025211000</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2861,11 +2881,7 @@
         <v>1</v>
       </c>
       <c r="L61" s="5" t="inlineStr"/>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -2881,7 +2897,11 @@
           <t>Andri Setiawan</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>199302222025211000</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2900,11 +2920,7 @@
         <v>1</v>
       </c>
       <c r="L62" s="5" t="inlineStr"/>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -2920,7 +2936,11 @@
           <t>Agus Feriyanto</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>199208152025211000</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2939,11 +2959,7 @@
         <v>1</v>
       </c>
       <c r="L63" s="5" t="inlineStr"/>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -2959,7 +2975,11 @@
           <t>M. Arif Prasetyo</t>
         </is>
       </c>
-      <c r="D64" s="5" t="n"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>199204162025211000</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -2978,11 +2998,7 @@
         <v>1</v>
       </c>
       <c r="L64" s="5" t="inlineStr"/>
-      <c r="M64" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -2998,7 +3014,11 @@
           <t>Agus Yahya</t>
         </is>
       </c>
-      <c r="D65" s="5" t="n"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>198308172025211000</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3017,11 +3037,7 @@
         <v>1</v>
       </c>
       <c r="L65" s="5" t="inlineStr"/>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
@@ -3037,7 +3053,11 @@
           <t>Joko Santoso</t>
         </is>
       </c>
-      <c r="D66" s="5" t="n"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>197706152025211000</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3056,11 +3076,7 @@
         <v>1</v>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -3076,7 +3092,11 @@
           <t>Dedi Irawan</t>
         </is>
       </c>
-      <c r="D67" s="5" t="n"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>199412182025211000</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3095,11 +3115,7 @@
         <v>1</v>
       </c>
       <c r="L67" s="5" t="inlineStr"/>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
@@ -3112,10 +3128,14 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Faisal</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n"/>
+          <t>Faisal Ramadan</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>200001052025211000</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3134,11 +3154,7 @@
         <v>1</v>
       </c>
       <c r="L68" s="5" t="inlineStr"/>
-      <c r="M68" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -3154,7 +3170,11 @@
           <t>Samsun Efendi</t>
         </is>
       </c>
-      <c r="D69" s="5" t="n"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>198810032025211000</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3173,11 +3193,7 @@
         <v>1</v>
       </c>
       <c r="L69" s="5" t="inlineStr"/>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
@@ -3193,7 +3209,11 @@
           <t>Sahrul</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>199709212025211000</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3212,11 +3232,7 @@
         <v>1</v>
       </c>
       <c r="L70" s="5" t="inlineStr"/>
-      <c r="M70" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -3232,7 +3248,11 @@
           <t>Amrulloh</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>198605102025211000</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3251,11 +3271,7 @@
         <v>1</v>
       </c>
       <c r="L71" s="5" t="inlineStr"/>
-      <c r="M71" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -3271,7 +3287,11 @@
           <t>Wardani</t>
         </is>
       </c>
-      <c r="D72" s="5" t="n"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>199411092025211000</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3290,11 +3310,7 @@
         <v>1</v>
       </c>
       <c r="L72" s="5" t="inlineStr"/>
-      <c r="M72" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -3310,7 +3326,11 @@
           <t>Ridho Kurnia</t>
         </is>
       </c>
-      <c r="D73" s="5" t="n"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>199606172025211000</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3329,11 +3349,7 @@
         <v>1</v>
       </c>
       <c r="L73" s="5" t="inlineStr"/>
-      <c r="M73" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
@@ -3341,18 +3357,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>staff-70</t>
+          <t>staff-71</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Gading Ade Nata, A.Md.Pt</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="n"/>
+          <t>Junaidi</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>1801090311950000</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -3368,11 +3388,7 @@
         <v>1</v>
       </c>
       <c r="L74" s="5" t="inlineStr"/>
-      <c r="M74" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -3380,15 +3396,19 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>staff-71</t>
+          <t>staff-72</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Junaidi</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="n"/>
+          <t>Ali Usman</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>199010152025211000</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3407,11 +3427,7 @@
         <v>1</v>
       </c>
       <c r="L75" s="5" t="inlineStr"/>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
@@ -3419,15 +3435,19 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>staff-72</t>
+          <t>staff-73</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Ali Usman</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="n"/>
+          <t>Alimun</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>198508162025211000</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3446,11 +3466,7 @@
         <v>1</v>
       </c>
       <c r="L76" s="5" t="inlineStr"/>
-      <c r="M76" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -3458,15 +3474,19 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>staff-73</t>
+          <t>staff-74</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Alimun</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n"/>
+          <t>M. Rusli</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>198208102025211000</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3485,11 +3505,7 @@
         <v>1</v>
       </c>
       <c r="L77" s="5" t="inlineStr"/>
-      <c r="M77" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -3497,15 +3513,19 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>staff-74</t>
+          <t>staff-76</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Rusli</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="n"/>
+          <t>M. Yoga Pratama</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>199711022025211000</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3524,11 +3544,7 @@
         <v>1</v>
       </c>
       <c r="L78" s="5" t="inlineStr"/>
-      <c r="M78" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -3536,18 +3552,22 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>staff-75</t>
+          <t>staff-77</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Solehah</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="n"/>
+          <t>Bagus Prasetio, A.Md.P</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>1801242912000000</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Umum</t>
+          <t>Layanan Rehabilitasi Sosial</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -3563,11 +3583,7 @@
         <v>1</v>
       </c>
       <c r="L79" s="5" t="inlineStr"/>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -3575,15 +3591,19 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>staff-76</t>
+          <t>staff-78</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>M. Yoga Pratama</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="n"/>
+          <t>Umam Wijaya</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>1801160411050000</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3602,11 +3622,7 @@
         <v>1</v>
       </c>
       <c r="L80" s="5" t="inlineStr"/>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -3614,18 +3630,22 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>staff-77</t>
+          <t>staff-79</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Bagus Prasetio, A.Md.P</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="n"/>
+          <t>Prayoga Stiawan</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>1801060707080010</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -3641,11 +3661,7 @@
         <v>1</v>
       </c>
       <c r="L81" s="5" t="inlineStr"/>
-      <c r="M81" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
@@ -3653,15 +3669,19 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>staff-78</t>
+          <t>staff-80</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Umam Wijaya</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="n"/>
+          <t>Ricky Randyca</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>3673010701040000</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
           <t>Umum</t>
@@ -3680,85 +3700,198 @@
         <v>1</v>
       </c>
       <c r="L82" s="5" t="inlineStr"/>
-      <c r="M82" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>staff-81</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Andriansyah Taufik H.S, S.Tr.Sos</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>1802160409990000</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Sosial</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Staf</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="n"/>
+      <c r="H83" s="6" t="n"/>
+      <c r="I83" s="6" t="n"/>
+      <c r="J83" s="6" t="n"/>
+      <c r="K83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="5" t="inlineStr"/>
+      <c r="M83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>staff-82</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Ajie Deo Risnaldi, Amd.Kep</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>1801101503040000</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Medis</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Staf</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="6" t="n"/>
+      <c r="I84" s="6" t="n"/>
+      <c r="J84" s="6" t="n"/>
+      <c r="K84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="5" t="inlineStr"/>
+      <c r="M84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="inlineStr">
+      <c r="A85" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>staff-83</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Firdana Saputra</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>1801101212030000</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Medis</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Staf</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="n"/>
+      <c r="H85" s="6" t="n"/>
+      <c r="I85" s="6" t="n"/>
+      <c r="J85" s="6" t="n"/>
+      <c r="K85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="5" t="inlineStr"/>
+      <c r="M85" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>AKUN SUPER ADMIN TERPISAH (DI LUAR DAFTAR 78 AKUN DI ATAS)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>Nama Lengkap</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>NIP/NIK</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>PIN</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Catatan</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>Super Admin Loka-Kin</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>0000000000000001</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>Akun sistem terpisah (bukan bagian 78 staf). Ganti NIP/NIK dengan identitas resmi bila sudah tersedia.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Nama dan NIP/NIK boleh diubah sebelum apply. Kosongkan NIP/NIK untuk melewati pembuatan akun Super Admin terpisah. Identitas awal ditandai placeholder agar tidak dipakai pada PDF kredensial pegawai.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M82"/>
+  <autoFilter ref="A4:M85"/>
   <mergeCells count="4">
-    <mergeCell ref="A85:M85"/>
+    <mergeCell ref="A92:M92"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A89:M89"/>
+    <mergeCell ref="A88:M88"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:K82">
+  <conditionalFormatting sqref="G5:K85">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>COUNTIF($G5:$K5,"1")&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:K82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan angka 1 pada satu kolom peran, atau biarkan kosong." type="list" errorStyle="stop">
+    <dataValidation sqref="G5:K85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan angka 1 pada satu kolom peran, atau biarkan kosong." type="list" errorStyle="stop">
       <formula1>"1"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3772,7 +3905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3842,35 +3975,39 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>staff-1</t>
+          <t>kepala-1</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Edwin, S.Sos</t>
+          <t>Heru Herlambang, S.AP</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>1801010101010001</t>
+          <t>198107192003121000</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>head</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Staf</t>
+          <t>Kepala Loka</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr"/>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Umum; Layanan Rehabilitasi Medis; Layanan Rehabilitasi Sosial; Clinical Supervisor</t>
+        </is>
+      </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3878,47 +4015,51 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>demo-preview</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21T12:32:46</t>
+          <t>2026-10-21T14:42:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>staff-2</t>
+          <t>staff-1</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Nurma Fitria, S.IP, M.IKom</t>
+          <t>Edwin, S.Sos</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>198611232010012008</t>
+          <t>197608242008011000</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Staf</t>
+          <t>Ketua Tim</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Umum</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>Layanan Rehabilitasi Sosial</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Sosial</t>
+        </is>
+      </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3931,24 +4072,24 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21T14:42:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>staff-3</t>
+          <t>staff-2</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>dr. Heni Purwanti</t>
+          <t>Nurma Fitria, S.IP, M.IKom</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>197501012005012003</t>
+          <t>198602262014032000</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -3963,12 +4104,12 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -3983,38 +4124,46 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21T11:51:26</t>
+          <t>2026-10-21T14:42:19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>staff-4</t>
+          <t>staff-3</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Saiful Bahri, A.Md.Kep</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
+          <t>dr. Heni Purwanti</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>199202112019022000</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Staf</t>
+          <t>Ketua Tim</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Sarana &amp; Prasarana</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
+          <t>Layanan Rehabilitasi Medis</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Medis</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4022,27 +4171,31 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>demo-preview</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21T14:42:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>staff-5</t>
+          <t>staff-4</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Okta Delvianita, AMKL, SE.</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
+          <t>Saiful Bahri, A.Md.Kep</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>198401012010011000</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4055,7 +4208,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Bendahara</t>
+          <t>Sarana &amp; Prasarana</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -4071,22 +4224,26 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21T14:42:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>staff-6</t>
+          <t>staff-5</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ns. Hamsah Prihadi Istianto, S.Kep</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
+          <t>Okta Delvianita, S.M</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>199010202014032000</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4099,7 +4256,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Clinical Supervisor</t>
+          <t>Bendahara</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -4122,31 +4279,39 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>staff-7</t>
+          <t>staff-6</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>dr. Utari Gita Mutiara</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
+          <t>Ns. Hamsah Prihadi Istianto, S.Kep</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>198902122014031000</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>clinical_supervisor</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Staf</t>
+          <t>Clinical Supervisor</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>Clinical Supervisor</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Umum; Layanan Rehabilitasi Medis; Layanan Rehabilitasi Sosial</t>
+        </is>
+      </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4159,22 +4324,26 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21T14:42:19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>staff-8</t>
+          <t>staff-7</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Yulina Destiani, A.Md.Kep</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
+          <t>dr. Utari Gita Mutiara</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>199107132020122000</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4210,17 +4379,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>staff-9</t>
+          <t>staff-8</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Daniel, A.Md.Kep</t>
+          <t>Yulina Destiani, A.Md.Kep</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>197804122006041005</t>
+          <t>199812122020122000</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -4235,7 +4404,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -4246,27 +4415,31 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>demo-preview</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21T11:51:26</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>staff-10</t>
+          <t>staff-9</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Yoga Adi Yuliawan, A.Md.Kes</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
+          <t>Daniel, A.Md.Kep</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>199008092020121000</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4290,27 +4463,31 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>demo-preview</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21T14:21:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>staff-11</t>
+          <t>staff-10</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Evi Soleha, A.Md.AK</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
+          <t>Yoga Adi Yuliawan, A.Md.Kes</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>199707272022031000</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4323,7 +4500,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -4346,15 +4523,19 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>staff-12</t>
+          <t>staff-11</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Nanda Alif Utama, A.Md.RAD</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
+          <t>Evi Soleha, A.Md.AK</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>199411102023212000</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4367,7 +4548,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -4390,15 +4571,19 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>staff-13</t>
+          <t>staff-12</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Risma Sefridasari, A.Md.KG</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
+          <t>Nanda Alif Utama, A.Md.RAD</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>199101202023211000</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4411,7 +4596,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Layanan Rehabilitasi Sosial</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -4434,15 +4619,19 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>staff-14</t>
+          <t>staff-13</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Tri Yunita, A.Md.Keb</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
+          <t>Risma Sefridasari, A.Md.KG</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>199008312023212000</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4478,15 +4667,19 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>staff-15</t>
+          <t>staff-14</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Dendi Purnama, S.Kep, Ns</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr"/>
+          <t>Tri Yunita, A.Md.Keb</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>199406222023212000</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4522,15 +4715,19 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>staff-16</t>
+          <t>staff-15</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Randy Simanjutak, A.Md.Gz</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr"/>
+          <t>Dendi Purnama, S.Kep, Ns</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>199012132023211000</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4566,15 +4763,19 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>staff-17</t>
+          <t>staff-16</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Ikke Asmawati, A.Md.KL</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr"/>
+          <t>Randy Simanjutak, A.Md.Gz</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>199105142023211000</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4587,7 +4788,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Perencanaan</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -4610,15 +4811,19 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>staff-18</t>
+          <t>staff-17</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>dr. Resti Adystia</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr"/>
+          <t>Ikke Asmawati, A.Md.KL</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>199512102023212000</t>
+        </is>
+      </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4631,7 +4836,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Medis</t>
+          <t>Perencanaan</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
@@ -4654,15 +4859,19 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>staff-19</t>
+          <t>staff-18</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Karunia Hadpha Saputri, A.Md.Keb</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr"/>
+          <t>dr. Resti Adystia</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>198709232023212000</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4698,15 +4907,19 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>staff-20</t>
+          <t>staff-19</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Wiria Ahaddillah, S.Kep, Ners</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
+          <t>Karunia Hadpha Saputri, A.Md.Keb</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>199012092023212000</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4742,15 +4955,19 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>staff-21</t>
+          <t>staff-20</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Heby Segapa, A.Md.Farm</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr"/>
+          <t>Wiria Ahaddillah, S.Kep, Ners</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>199501082023211000</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4786,15 +5003,19 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>staff-22</t>
+          <t>staff-21</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Febri Ardiyansyah, AMF</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr"/>
+          <t>Heby Segapa, A.Md.Farm</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>199005072023211000</t>
+        </is>
+      </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4830,15 +5051,19 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>staff-23</t>
+          <t>staff-22</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Anggi Oktaria, A.Md.Ft</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr"/>
+          <t>Febri Ardiyansyah, AMF</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>199302112023211000</t>
+        </is>
+      </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4874,15 +5099,19 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>staff-24</t>
+          <t>staff-23</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Pika Junetthy BR Pinem, A.Md.Gz</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
+          <t>Anggi Oktaria, A.Md.Ft</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>199810062023212000</t>
+        </is>
+      </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4918,15 +5147,19 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>staff-25</t>
+          <t>staff-24</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Galuh Dwi Satria Vianto, A.Md.Kep</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr"/>
+          <t>Pika Junetthy BR Pinem, A.Md.Gz</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>199606072023212000</t>
+        </is>
+      </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4939,7 +5172,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Layanan Rehabilitasi Medis</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -4962,15 +5195,19 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>staff-26</t>
+          <t>staff-25</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Yessy Lisnawati, SE</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr"/>
+          <t>Galuh Dwi Satria Vianto, A.Md.Kep</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>199203122023211000</t>
+        </is>
+      </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -4983,7 +5220,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Umum</t>
+          <t>Layanan Rehabilitasi Sosial</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
@@ -5006,15 +5243,19 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>staff-27</t>
+          <t>staff-26</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Yudian Pratama Putra, S.M</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr"/>
+          <t>Yessy Lisnawati, SE</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>198811212025212000</t>
+        </is>
+      </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5050,15 +5291,19 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>staff-28</t>
+          <t>staff-27</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Restivo Nandami, A.Md</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr"/>
+          <t>Yudian Pratama Putra, S.M</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>199409292025211000</t>
+        </is>
+      </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5094,15 +5339,19 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>staff-29</t>
+          <t>staff-28</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Heti Liswati</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr"/>
+          <t>Restivo Nandami, A.Md</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>199109022025212000</t>
+        </is>
+      </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5138,15 +5387,19 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>staff-30</t>
+          <t>staff-29</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Riza Rimayanti</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr"/>
+          <t>Heti Liswati</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>199404142025212000</t>
+        </is>
+      </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5182,15 +5435,19 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>staff-31</t>
+          <t>staff-30</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Denda Nopriawan Putra</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr"/>
+          <t>Riza Rimayanti</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>199404012025212000</t>
+        </is>
+      </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5226,15 +5483,19 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>staff-32</t>
+          <t>staff-31</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Ahmad Soleh, S.Kom</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr"/>
+          <t>Denda Nopriawan Putra</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>198911182025211000</t>
+        </is>
+      </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5270,15 +5531,19 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>staff-33</t>
+          <t>staff-32</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Amardin Fikri, A.Md</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr"/>
+          <t>Ahmad Soleh, S.Kom</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>199106242025211000</t>
+        </is>
+      </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5314,15 +5579,19 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>staff-34</t>
+          <t>staff-33</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Evi Talia, A.Md</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr"/>
+          <t>Amardin Fikri, A.Md</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>198912072025211000</t>
+        </is>
+      </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5358,15 +5627,19 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>staff-35</t>
+          <t>staff-34</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Eka Rahma Saputri</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
+          <t>Evi Talia, A.Md</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>199412092025212000</t>
+        </is>
+      </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5402,15 +5675,19 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>staff-36</t>
+          <t>staff-35</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Indra Gunawan</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
+          <t>Eka Rahma Saputri</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>1801064911980010</t>
+        </is>
+      </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5423,7 +5700,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
@@ -5446,15 +5723,19 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>staff-37</t>
+          <t>staff-36</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Amelia, A.Md.Kep</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
+          <t>Indra Gunawan</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>198809152025211000</t>
+        </is>
+      </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5490,15 +5771,19 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>staff-38</t>
+          <t>staff-37</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Adams Resmitha Thalib, SE</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr"/>
+          <t>Amelia, A.Md.Kep</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>199805032025212000</t>
+        </is>
+      </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5534,12 +5819,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>staff-39</t>
+          <t>staff-38</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Arisman</t>
+          <t>Adams Resmitha Thalib, SE</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
@@ -5578,15 +5863,19 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>staff-40</t>
+          <t>staff-39</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Rizal, S.Psi</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr"/>
+          <t>Arisman</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>198804112025211000</t>
+        </is>
+      </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5622,15 +5911,19 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>staff-41</t>
+          <t>staff-40</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Yoga Eko Budiyanto</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr"/>
+          <t>Rizal, S.Psi</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>199510122025211000</t>
+        </is>
+      </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5666,15 +5959,19 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>staff-42</t>
+          <t>staff-41</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Raga Dwindo Pangestu</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr"/>
+          <t>Yoga Eko Budiyanto</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>199412292025211000</t>
+        </is>
+      </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5710,15 +6007,19 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>staff-43</t>
+          <t>staff-42</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Wendy Ramarten, S.Pd</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr"/>
+          <t>Raga Dwindo Pangestu</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>199705052025211000</t>
+        </is>
+      </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5754,15 +6055,19 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>staff-44</t>
+          <t>staff-43</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Yoyon Saputra, S.Sos</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr"/>
+          <t>Wendy Ramarten, S.Pd</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>199608132025211000</t>
+        </is>
+      </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5806,7 +6111,11 @@
           <t>Indra Ibnul Alhibi Ramadhani, A.Md.Pi</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>1871131412000010</t>
+        </is>
+      </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5850,7 +6159,11 @@
           <t>Emi Rosmiko Sari, A.Md.Kep</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr"/>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>198206112025212000</t>
+        </is>
+      </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5894,7 +6207,11 @@
           <t>Saiful Hamdani, S.Psi</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr"/>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>1871131508000000</t>
+        </is>
+      </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5938,7 +6255,11 @@
           <t>M. Nur Hidayatullah</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr"/>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>198607132025211000</t>
+        </is>
+      </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5982,7 +6303,11 @@
           <t>Yusuf Arief Sena K, S.Psi</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr"/>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>1871030806990000</t>
+        </is>
+      </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6026,7 +6351,11 @@
           <t>Suci Ramadani, AMKL</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr"/>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>199004122025212000</t>
+        </is>
+      </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6070,7 +6399,11 @@
           <t>Nadia Maulidia, A.Md.RMIK</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr"/>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>1801065605020000</t>
+        </is>
+      </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6114,7 +6447,11 @@
           <t>Nur Cholish</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr"/>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>198312282025211000</t>
+        </is>
+      </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6158,7 +6495,11 @@
           <t>Gunawan Adi Saputra</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr"/>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>199211112025211000</t>
+        </is>
+      </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6202,7 +6543,11 @@
           <t>Saipul Bahri</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr"/>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>198505022025211000</t>
+        </is>
+      </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6246,7 +6591,11 @@
           <t>Septila Damirza</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr"/>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>199509052025211000</t>
+        </is>
+      </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6290,7 +6639,11 @@
           <t>Ma'ruf Nufri Ismail</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr"/>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>198711232025211000</t>
+        </is>
+      </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6334,7 +6687,11 @@
           <t>Mukhsinin</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr"/>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>199412122025211000</t>
+        </is>
+      </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6378,7 +6735,11 @@
           <t>Andri Setiawan</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr"/>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>199302222025211000</t>
+        </is>
+      </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6422,7 +6783,11 @@
           <t>Agus Feriyanto</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>199208152025211000</t>
+        </is>
+      </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6466,7 +6831,11 @@
           <t>M. Arif Prasetyo</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr"/>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>199204162025211000</t>
+        </is>
+      </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6510,7 +6879,11 @@
           <t>Agus Yahya</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr"/>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>198308172025211000</t>
+        </is>
+      </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6554,7 +6927,11 @@
           <t>Joko Santoso</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr"/>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>197706152025211000</t>
+        </is>
+      </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6598,7 +6975,11 @@
           <t>Dedi Irawan</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>199412182025211000</t>
+        </is>
+      </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6639,10 +7020,14 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Faisal</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr"/>
+          <t>Faisal Ramadan</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>200001052025211000</t>
+        </is>
+      </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6686,7 +7071,11 @@
           <t>Samsun Efendi</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr"/>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>198810032025211000</t>
+        </is>
+      </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6730,7 +7119,11 @@
           <t>Sahrul</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr"/>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>199709212025211000</t>
+        </is>
+      </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6774,7 +7167,11 @@
           <t>Amrulloh</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr"/>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>198605102025211000</t>
+        </is>
+      </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6818,7 +7215,11 @@
           <t>Wardani</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>199411092025211000</t>
+        </is>
+      </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6862,7 +7263,11 @@
           <t>Ridho Kurnia</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>199606172025211000</t>
+        </is>
+      </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6898,15 +7303,19 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>staff-70</t>
+          <t>staff-71</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Gading Ade Nata, A.Md.Pt</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr"/>
+          <t>Junaidi</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>1801090311950000</t>
+        </is>
+      </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6919,7 +7328,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
@@ -6942,15 +7351,19 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>staff-71</t>
+          <t>staff-72</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Junaidi</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr"/>
+          <t>Ali Usman</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>199010152025211000</t>
+        </is>
+      </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -6986,15 +7399,19 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>staff-72</t>
+          <t>staff-73</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Ali Usman</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr"/>
+          <t>Alimun</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>198508162025211000</t>
+        </is>
+      </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -7030,15 +7447,19 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>staff-73</t>
+          <t>staff-74</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Alimun</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr"/>
+          <t>M. Rusli</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>198208102025211000</t>
+        </is>
+      </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -7074,15 +7495,19 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>staff-74</t>
+          <t>staff-76</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Rusli</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr"/>
+          <t>M. Yoga Pratama</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>199711022025211000</t>
+        </is>
+      </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -7118,15 +7543,19 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>staff-75</t>
+          <t>staff-77</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Solehah</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr"/>
+          <t>Bagus Prasetio, A.Md.P</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>1801242912000000</t>
+        </is>
+      </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -7139,7 +7568,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Umum</t>
+          <t>Layanan Rehabilitasi Sosial</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr"/>
@@ -7162,15 +7591,19 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>staff-76</t>
+          <t>staff-78</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>M. Yoga Pratama</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr"/>
+          <t>Umam Wijaya</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>1801160411050000</t>
+        </is>
+      </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -7206,15 +7639,19 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>staff-77</t>
+          <t>staff-79</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Bagus Prasetio, A.Md.P</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr"/>
+          <t>Prayoga Stiawan</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>1801060707080010</t>
+        </is>
+      </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -7227,7 +7664,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Layanan Rehabilitasi Sosial</t>
+          <t>Umum</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -7250,15 +7687,19 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>staff-78</t>
+          <t>staff-80</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Umam Wijaya</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr"/>
+          <t>Ricky Randyca</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>3673010701040000</t>
+        </is>
+      </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -7291,8 +7732,152 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>staff-81</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Andriansyah Taufik H.S, S.Tr.Sos</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>1802160409990000</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Staf</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Sosial</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>staff-82</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Ajie Deo Risnaldi, Amd.Kep</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>1801101503040000</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Staf</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Medis</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>staff-83</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Firdana Saputra</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>1801101212030000</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Staf</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Layanan Rehabilitasi Medis</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J79"/>
+  <autoFilter ref="A1:J82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7369,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>0</v>
@@ -7381,7 +7966,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -7422,13 +8007,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>1</v>
@@ -7453,10 +8038,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -7475,13 +8060,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -7550,13 +8135,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>36</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -7569,19 +8154,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Clustering-Akun-LokaKin.xlsx
+++ b/Clustering-Akun-LokaKin.xlsx
@@ -2156,7 +2156,11 @@
           <t>Adams Resmitha Thalib, SE</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n"/>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>198305192025211000</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Layanan Rehabilitasi Sosial</t>
@@ -2175,11 +2179,7 @@
         <v>1</v>
       </c>
       <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>NIP/NIK belum ada — wajib diisi agar akun dapat login.</t>
-        </is>
-      </c>
+      <c r="M43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -5827,7 +5827,11 @@
           <t>Adams Resmitha Thalib, SE</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>198305192025211000</t>
+        </is>
+      </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
           <t>staff</t>
@@ -5851,12 +5855,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>roster-sync</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21T14:49:04</t>
         </is>
       </c>
     </row>
